--- a/data/exports/王颖瑜伽/dist_order_2026-09-29.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-09-29.xlsx
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>💖海霞💖</t>
+          <t>💖越来越好💖</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
